--- a/sample_data/file4.xlsx
+++ b/sample_data/file4.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t xml:space="preserve">NAME</t>
   </si>
   <si>
-    <t xml:space="preserve">EMAIL</t>
+    <t xml:space="preserve">EMAIL_ADDRESS</t>
   </si>
   <si>
     <t xml:space="preserve">dexter</t>
@@ -38,6 +38,12 @@
   </si>
   <si>
     <t xml:space="preserve">doha@example.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ishaq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ishaq@example.com</t>
   </si>
 </sst>
 </file>
@@ -47,11 +53,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="DejaVu Sans"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -73,6 +80,14 @@
       <color rgb="FF0000FF"/>
       <name val="DejaVu Sans"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="DejaVu Sans"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -117,12 +132,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -249,37 +272,46 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultColWidth="10.08203125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" display="dexter@example.com"/>
     <hyperlink ref="B3" r:id="rId2" display="doha@example.com"/>
+    <hyperlink ref="B5" r:id="rId3" display="ishaq@example.com"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
